--- a/data/excel/audit_log.xlsx
+++ b/data/excel/audit_log.xlsx
@@ -944,6 +944,591 @@
   </x:si>
   <x:si>
     <x:t>0HNMOJK8496O5:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b5e2ed52-cf25-4694-bde4-e8ca627ea647</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T12:41:01.4700060Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>::ffff:172.19.0.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mozilla/5.0 (Windows NT 10.0; Win64; x64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/148.0.0.0 Safari/537.36 OPR/132.0.0.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMF3:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8302e97f-52d5-4f47-acb4-ca7fcca16d72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T12:43:49.0696096Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>user.locked</x:t>
+  </x:si>
+  <x:si>
+    <x:t>False</x:t>
+  </x:si>
+  <x:si>
+    <x:t>True</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bloqueo de usuario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMHK:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9b1bf9e3-db4b-41a4-a47c-b6f016fb1e7b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T12:43:50.8015256Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>user.unlocked</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Desbloqueo de usuario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMHL:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11750a85-a09e-4132-90a1-de4be830eeb2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T12:47:13.8510446Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMHR:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03ec0142-abf8-4482-acb2-eea73102dc1a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T12:47:22.5622048Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>auth.login_failed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>false</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Credenciales invalidas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMHS:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7eaf6f8b-800c-447e-9d7d-16e48012b9c0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T12:48:06.4646546Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMHT:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9d41b378-84f2-43ea-95bc-9d9f9b8f72c2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T12:48:29.4494913Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMHU:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cf28d1d0-7193-4d01-9cb4-a2bb946eed46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T12:48:44.5649181Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMI2:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a4e51808-550b-4d96-8a0e-f06d9ebe833b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T12:49:06.7405301Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nico.rod26@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMI3:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>416f46ee-705c-49ad-aa0c-48812516b9db</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T12:49:37.9167975Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMI4:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ef3d2b7d-f04e-4998-a7d5-8c0ac044cd82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T13:41:22.1809661Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mozilla/5.0 (Linux; Android 10; K) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/149.0.0.0 Mobile Safari/537.36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMI5:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b6c9fa91-a4bb-495b-8f76-cea906400053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T13:41:38.4393115Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>admin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMI6:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>e25a14e9-c4fc-4ec8-a40c-ddf4b197e810</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T13:42:12.9211158Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMI7:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>e3c3b81f-5315-4775-8e58-58a679179ec1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T13:55:28.0422202Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSTOLBVMJJ:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86d0adc4-47ac-4964-b6fb-5a1735181690</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T14:39:39.7709516Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMSVQUF3TU0:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b9e338a0-684d-4485-958f-871128338760</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T15:44:13.2997942Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M0T0:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>c24c4df8-f7f3-42f6-9d8f-675b3b2285c7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T15:59:47.9029630Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CFA-1000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"Codigo":"CFA-1000","Nombre":"AUGER-1000","FaenaCodigo":"FAE_ESP","TipoActivo":"CFA","Estado":"Active","UbicacionTecnicaCodigo":"SERV-04-07","Familia":"Cami\u00F3n F\u00E1brica","Marca":"ASTRA","Modelo":"HD9 84.48","Patente":"TWCK-41","NumeroSerie":"ZCNH98432SPC13094","Propiedad":"Propio","Criticidad":"Media","EstadoDocumental":"Pendiente","EstadoOperacional":"Operativo","FichaTecnicaJson":null,"FichaValidada":"false","FechaAlta":"2026-07-08T15:59:47.8384370Z","FechaActualizacion":"2026-07-08T15:59:47.8384370Z","CompletitudFicha":"100"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M0T8:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6c2c41d8-01e1-494a-b2d7-e048a3daf1ec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T16:01:46.0893052Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRUEBA-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAE_AND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"Codigo":"PRUEBA-2","Nombre":"prueba-2","FaenaCodigo":"FAE_AND","TipoActivo":"prueba","Estado":"Unavailable","UbicacionTecnicaCodigo":"SERV-04-18","Familia":null,"Marca":null,"Modelo":null,"Patente":null,"NumeroSerie":null,"Propiedad":"Propio","Criticidad":"Media","EstadoDocumental":"Pendiente","EstadoOperacional":"Operativo","FichaTecnicaJson":null,"FichaValidada":"false","FechaAlta":"2026-07-08T16:01:46.0338399Z","FechaActualizacion":"2026-07-08T16:01:46.0338399Z","CompletitudFicha":"64"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M0U2:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>f16df7d6-4d76-4f42-9131-ed362915c897</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T16:02:20.4936203Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StateChanged</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unavailable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test de cambios</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M0UB:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a0e71ce6-2c2d-40bd-9f73-345d87084663</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T16:02:41.9601322Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"Codigo":"PRUEBA-2","Nombre":"prueba-2","FaenaCodigo":"FAE_AND","TipoActivo":"prueba","Estado":"Unavailable","UbicacionTecnicaCodigo":"SERV-04-18","Familia":"","Marca":"","Modelo":"","Patente":"","NumeroSerie":"","Propiedad":"Propio","Criticidad":"Media","EstadoDocumental":"Pendiente","EstadoOperacional":"No disponible","CompletitudFicha":"64","FichaValidada":"false","FichaTecnicaJson":"","FechaAlta":"2026-07-08T16:01:46.0338399Z","FechaActualizacion":"2026-07-08T16:02:20.3901899Z"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"Codigo":"PRUEBA-2","Nombre":"prueba-2","FaenaCodigo":"FAE_AND","TipoActivo":"prueba","Estado":"Unavailable","UbicacionTecnicaCodigo":"SERV-04-18","Familia":"prueba","Marca":null,"Modelo":null,"Patente":null,"NumeroSerie":null,"Propiedad":"Propio","Criticidad":"Media","EstadoDocumental":"Pendiente","EstadoOperacional":"No disponible","FichaTecnicaJson":null,"FichaValidada":"false","FechaAlta":"2026-07-08T16:01:46.0338399Z","FechaActualizacion":"2026-07-08T16:02:41.8812330Z","CompletitudFicha":"73"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M0UJ:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4a91cc1e-702d-442d-ba64-83af74f4118f</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T16:03:02.9094092Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M0UR:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>073c9d9a-579c-41c7-b93e-b781eb3f153a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T16:06:32.4351048Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"Codigo":"CFA-1000","Nombre":"AUGER-1000","FaenaCodigo":"FAE_ESP","TipoActivo":"CFA","Estado":"Active","UbicacionTecnicaCodigo":"SERV-04-07","Familia":"Cami\u00F3n F\u00E1brica","Marca":"ASTRA","Modelo":"HD9 84.48","Patente":"TWCK-41","NumeroSerie":"ZCNH98432SPC13094","Propiedad":"Propio","Criticidad":"Media","EstadoDocumental":"Pendiente","EstadoOperacional":"Operativo","CompletitudFicha":"100","FichaValidada":"false","FichaTecnicaJson":"","FechaAlta":"2026-07-08T15:59:47.8384370Z","FechaActualizacion":"2026-07-08T15:59:47.8384370Z"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"Codigo":"CFA-1000","Nombre":"AUGER-1000","FaenaCodigo":"FAE_ESP","TipoActivo":"CFA","Estado":"Active","UbicacionTecnicaCodigo":"SERV-04-07","Familia":"Cami\u00F3n F\u00E1brica","Marca":"ASTRA","Modelo":"HD9 84.48","Patente":"TWCK-41","NumeroSerie":null,"Propiedad":"Propio","Criticidad":"Media","EstadoDocumental":"Pendiente","EstadoOperacional":"Operativo","FichaTecnicaJson":null,"FichaValidada":"false","FechaAlta":"2026-07-08T15:59:47.8384370Z","FechaActualizacion":"2026-07-08T16:06:32.3858031Z","CompletitudFicha":"91"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M0VN:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a28ee74b-2844-4242-b58c-398fa2232092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T16:15:43.4391092Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRUEBA-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAE_ESV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"Codigo":"PRUEBA-3","Nombre":"prueba-3","FaenaCodigo":"FAE_ESV","TipoActivo":"prueba","Estado":"Active","UbicacionTecnicaCodigo":"SERV-04-19","Familia":null,"Marca":null,"Modelo":null,"Patente":null,"NumeroSerie":null,"Propiedad":"Propio","Criticidad":"Media","EstadoDocumental":"Pendiente","EstadoOperacional":"Operativo","FichaTecnicaJson":null,"FichaValidada":"false","FechaAlta":"2026-07-08T16:15:43.3865096Z","FechaActualizacion":"2026-07-08T16:15:43.3865096Z","CompletitudFicha":"64"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M103:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1e1f8b53-f1f7-4123-a5b1-26f85d195b03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T16:50:58.6650044Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M10R:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a62b744e-3fd6-4aca-adcf-837a72d9698b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T17:54:51.9594537Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>::ffff:172.19.0.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thunder Client (https://www.thunderclient.com)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M11S:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29092306-f37f-43bb-a78d-adfa5f0a1ab8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T17:57:36.8617380Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M120:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01cbe8ec-6eac-4444-a558-825ec7e13251</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T17:58:09.0498398Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M126:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7a94b958-2d5a-43b1-bbba-8c059254a60c</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T17:58:10.5856440Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M127:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47a23e55-0dde-4ce8-abee-96377023db07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:03:01.2725429Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0c3f83fc-b1f1-43e9-88ab-433765280bcf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bod1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M128:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>f14ea9e1-e14f-4c26-a62e-bfd957b0c107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:03:20.8667713Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M12A:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31ec2032-0138-4a9f-88bc-1bb6d3476075</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:03:30.4270537Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M12B:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>f8361bc2-bbc5-4ba4-98be-3a45db84f479</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:04:07.0287706Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M13S:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9eaade5b-2735-42fa-81e2-2a6277d23ba1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:04:26.4706163Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M13T:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>f35a5969-9633-472a-a1f4-ba545f9990dd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:05:16.4634211Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>e4447694-c49f-456f-abb0-35a9de1ecfa4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>con1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M143:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a63908f6-d886-4f49-b4ef-06609a411320</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:05:23.4408746Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>user.roles_changed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Critical</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bodeguero;consulta_faena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bodeguero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cambio de roles</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M145:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>d0a608fd-38cc-4fdd-874c-268b56e30fbf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:05:59.8860515Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3ad6aace-1fa6-416a-bf09-6b3b30bbc257</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ger1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M146:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dbd28f89-9395-499c-96a4-5badde6e5907</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:07:19.2325567Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9ac69b51-fe10-40c2-b52d-fb957af6e993</x:t>
+  </x:si>
+  <x:si>
+    <x:t>plani1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M148:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3510b781-aa81-4502-9da6-a6df0ad76afb</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:08:11.9496791Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>866e5098-0afe-4069-8acb-ccf90d054722</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sup_b1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M14A:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8606b4d6-b39c-4cee-8237-6a39e9871e93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:09:06.5188500Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>589f4e25-1197-4a91-b06d-68c963f7db4b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sup_m1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M14C:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53e8dbb7-fac1-4aae-b12d-ec8268416e1f</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:09:37.0422297Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a9a0b7c8-87e8-4ce6-ad0b-777b2d733883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M14E:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>d8a1938f-4fed-4b67-b62c-ed52d8fa6d64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:10:15.5478373Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M14G:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3232134f-909d-49b3-8499-afc12eddd855</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:10:23.7652005Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M14H:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4bdcc9db-787c-4a6b-a8f1-88260da2ba06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:11:07.9343463Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M153:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b4b43399-9bee-4272-9225-9c4b9d8699f6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:11:22.0501489Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M154:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20f19937-e066-4d94-95f7-b75e346f90bf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:12:10.9732712Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M169:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9171d432-62ad-4155-bc0d-d35bed5160c5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:12:46.2941393Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M16A:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a04f5efb-c7c9-4060-a6ee-c30729da6b48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:15:05.3828663Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M16F:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>647122fa-2ca1-4b02-be0e-11a5a045bbfa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:15:11.2949927Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M16G:00000001</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1309,7 +1894,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S78"/>
+  <x:dimension ref="A1:S126"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.139196" style="0" customWidth="1"/>
@@ -1323,7 +1908,7 @@
     <x:col min="9" max="9" width="8.567768" style="0" customWidth="1"/>
     <x:col min="10" max="11" width="255" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="14.282054" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="105.567768" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="119.139196" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="27.996339" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="7.853482" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="132.853482" style="0" customWidth="1"/>
@@ -4394,6 +4979,2070 @@
         <x:v>309</x:v>
       </x:c>
     </x:row>
+    <x:row r="79" spans="1:19">
+      <x:c r="A79" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F79" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G79" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I79" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L79" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M79" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O79" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q79" s="0" t="s">
+        <x:v>314</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:19">
+      <x:c r="A80" s="0" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F80" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G80" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I80" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J80" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="K80" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="L80" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M80" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="N80" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="O80" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q80" s="0" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="R80" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="S80" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:19">
+      <x:c r="A81" s="0" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F81" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G81" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I81" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J81" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="K81" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="L81" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M81" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="N81" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="O81" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q81" s="0" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="R81" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="S81" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:19">
+      <x:c r="A82" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F82" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G82" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I82" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L82" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M82" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O82" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q82" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:19">
+      <x:c r="A83" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F83" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G83" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I83" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="L83" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M83" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O83" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="P83" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="Q83" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:19">
+      <x:c r="A84" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F84" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G84" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I84" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="L84" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M84" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O84" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="P84" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="Q84" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:19">
+      <x:c r="A85" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E85" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F85" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G85" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I85" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L85" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M85" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O85" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q85" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:19">
+      <x:c r="A86" s="0" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F86" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G86" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I86" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L86" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M86" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O86" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q86" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:19">
+      <x:c r="A87" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="E87" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F87" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G87" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="I87" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="L87" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M87" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O87" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="P87" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="Q87" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:19">
+      <x:c r="A88" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F88" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G88" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I88" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L88" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M88" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O88" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q88" s="0" t="s">
+        <x:v>351</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:19">
+      <x:c r="A89" s="0" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F89" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G89" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I89" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="L89" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M89" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="O89" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="P89" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="Q89" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:19">
+      <x:c r="A90" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F90" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G90" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="I90" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="L90" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M90" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="O90" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="P90" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="Q90" s="0" t="s">
+        <x:v>359</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:19">
+      <x:c r="A91" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E91" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F91" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G91" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I91" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L91" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M91" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="O91" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q91" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:19">
+      <x:c r="A92" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E92" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F92" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G92" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I92" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L92" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M92" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="O92" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q92" s="0" t="s">
+        <x:v>365</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:19">
+      <x:c r="A93" s="0" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E93" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F93" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G93" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I93" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L93" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M93" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O93" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q93" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:19">
+      <x:c r="A94" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E94" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F94" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G94" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I94" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L94" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M94" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O94" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q94" s="0" t="s">
+        <x:v>371</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:19">
+      <x:c r="A95" s="0" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E95" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F95" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G95" s="0" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="H95" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="I95" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="K95" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="L95" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M95" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O95" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P95" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="Q95" s="0" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="S95" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:19">
+      <x:c r="A96" s="0" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E96" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F96" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G96" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="H96" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="I96" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="K96" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="L96" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M96" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O96" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P96" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="Q96" s="0" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="S96" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:19">
+      <x:c r="A97" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="E97" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G97" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="H97" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="I97" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J97" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="K97" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="L97" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M97" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O97" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P97" s="0" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="Q97" s="0" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="R97" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="S97" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:19">
+      <x:c r="A98" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="E98" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F98" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G98" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="H98" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="I98" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="J98" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="K98" s="0" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="L98" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M98" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O98" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P98" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="Q98" s="0" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="R98" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="S98" s="0" t="s">
+        <x:v>392</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:19">
+      <x:c r="A99" s="0" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="E99" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F99" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G99" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="H99" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="I99" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J99" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="K99" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="L99" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M99" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O99" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P99" s="0" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="Q99" s="0" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="R99" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="S99" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:19">
+      <x:c r="A100" s="0" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="E100" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F100" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G100" s="0" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="H100" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="I100" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="J100" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="K100" s="0" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="L100" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M100" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O100" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P100" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="Q100" s="0" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="R100" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="S100" s="0" t="s">
+        <x:v>401</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:19">
+      <x:c r="A101" s="0" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E101" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F101" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G101" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="H101" s="0" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="I101" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="K101" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="L101" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M101" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O101" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P101" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="Q101" s="0" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="S101" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:19">
+      <x:c r="A102" s="0" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E102" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F102" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G102" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I102" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L102" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M102" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O102" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q102" s="0" t="s">
+        <x:v>411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:19">
+      <x:c r="A103" s="0" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E103" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F103" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G103" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I103" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L103" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="M103" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="O103" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q103" s="0" t="s">
+        <x:v>416</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:19">
+      <x:c r="A104" s="0" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D104" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E104" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F104" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G104" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I104" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L104" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M104" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O104" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q104" s="0" t="s">
+        <x:v>419</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:19">
+      <x:c r="A105" s="0" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="E105" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F105" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G105" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I105" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J105" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="K105" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="L105" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M105" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="N105" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="O105" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q105" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="R105" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="S105" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:19">
+      <x:c r="A106" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="E106" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F106" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G106" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I106" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J106" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="K106" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="L106" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M106" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="N106" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="O106" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q106" s="0" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="R106" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="S106" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:19">
+      <x:c r="A107" s="0" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E107" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F107" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G107" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="I107" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K107" s="0" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="L107" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M107" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O107" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q107" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="S107" s="0" t="s">
+        <x:v>429</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:19">
+      <x:c r="A108" s="0" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E108" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F108" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G108" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I108" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L108" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M108" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O108" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q108" s="0" t="s">
+        <x:v>433</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:19">
+      <x:c r="A109" s="0" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E109" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F109" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G109" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="I109" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L109" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M109" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O109" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q109" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:19">
+      <x:c r="A110" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E110" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F110" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G110" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="I110" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L110" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M110" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O110" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q110" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:19">
+      <x:c r="A111" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E111" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F111" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G111" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I111" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L111" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M111" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O111" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q111" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:19">
+      <x:c r="A112" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E112" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F112" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G112" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="I112" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K112" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="L112" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M112" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O112" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q112" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="S112" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:19">
+      <x:c r="A113" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="E113" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F113" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G113" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="I113" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="J113" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="K113" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="L113" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M113" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="N113" s="0" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="O113" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q113" s="0" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="R113" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="S113" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:19">
+      <x:c r="A114" s="0" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C114" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D114" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E114" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F114" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G114" s="0" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="I114" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K114" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="L114" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M114" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O114" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q114" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="S114" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:19">
+      <x:c r="A115" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E115" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F115" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G115" s="0" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="I115" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K115" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="L115" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M115" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O115" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q115" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="S115" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:19">
+      <x:c r="A116" s="0" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E116" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F116" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G116" s="0" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="I116" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K116" s="0" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="L116" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M116" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O116" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q116" s="0" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="S116" s="0" t="s">
+        <x:v>469</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:19">
+      <x:c r="A117" s="0" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E117" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F117" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G117" s="0" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="I117" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K117" s="0" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="L117" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M117" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O117" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q117" s="0" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="S117" s="0" t="s">
+        <x:v>474</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:19">
+      <x:c r="A118" s="0" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E118" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F118" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G118" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="I118" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K118" s="0" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="L118" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M118" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O118" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q118" s="0" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="S118" s="0" t="s">
+        <x:v>479</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:19">
+      <x:c r="A119" s="0" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E119" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F119" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G119" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I119" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L119" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M119" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O119" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q119" s="0" t="s">
+        <x:v>483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:19">
+      <x:c r="A120" s="0" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E120" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F120" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G120" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="I120" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L120" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M120" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O120" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q120" s="0" t="s">
+        <x:v>486</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:19">
+      <x:c r="A121" s="0" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E121" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F121" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G121" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="I121" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L121" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M121" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O121" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q121" s="0" t="s">
+        <x:v>489</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:19">
+      <x:c r="A122" s="0" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E122" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F122" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G122" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I122" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L122" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M122" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O122" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q122" s="0" t="s">
+        <x:v>492</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:19">
+      <x:c r="A123" s="0" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E123" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F123" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G123" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I123" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L123" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M123" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O123" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q123" s="0" t="s">
+        <x:v>495</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:19">
+      <x:c r="A124" s="0" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E124" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F124" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G124" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="I124" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L124" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M124" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O124" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q124" s="0" t="s">
+        <x:v>498</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:19">
+      <x:c r="A125" s="0" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E125" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F125" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G125" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="I125" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L125" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M125" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O125" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q125" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:19">
+      <x:c r="A126" s="0" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E126" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F126" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G126" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I126" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L126" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M126" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O126" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q126" s="0" t="s">
+        <x:v>504</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/excel/audit_log.xlsx
+++ b/data/excel/audit_log.xlsx
@@ -1529,6 +1529,180 @@
   </x:si>
   <x:si>
     <x:t>0HNMT0D92M16G:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b35fb138-f379-4639-9350-b11af9c96b29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T19:18:30.6412215Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M183:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ec6a8125-39e7-4e00-b8b0-ff05e9fc5eeb</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T19:40:08.5211017Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>work_notification.created</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AvisosTrabajo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WorkNotification</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AV-000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"AvisoId":"AV-000001","Estado":"Creado","Tipo":"ApoyoOperacional","FaenaCodigo":"FAE_AND","ActivoCodigo":"PRUEBA-2","Sistema":null,"Subsistema":null,"Componente":null,"Descripcion":"prueba de hu 4","Prioridad":"Alta","Criticidad":"Media","Solicitante":"1dc348ae-ab97-4182-a1e4-b29d684dde2a","EvidenciaInicial":null,"FechaDeteccion":"2026-06-30T00:00:00.0000000Z","FechaCreacion":"2026-07-08T19:40:08.4718108Z","ClasificacionFalla":"ConRestriccion","EvaluadoPor":null,"EvaluadoEnUtc":null,"AprobadoPor":null,"AprobadoEnUtc":null,"RechazadoPor":null,"RechazadoEnUtc":null,"MotivoRechazo":null,"AnuladoPor":null,"AnuladoEnUtc":null,"MotivoAnulacion":null,"NumeroOT":null,"ConvertidoPor":null,"ConvertidoEnUtc":null,"Observaciones":"Aviso creado en CMMS"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>prueba de hu 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M1B9:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>977bbd35-aa9d-4a8d-8eef-85f0f72fcc9f</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T19:44:04.7785694Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>work_notification.approved</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"AvisoId":"AV-000001","Estado":"Creado","Tipo":"ApoyoOperacional","FaenaCodigo":"FAE_AND","ActivoCodigo":"PRUEBA-2","Sistema":"","Subsistema":"","Componente":"","Descripcion":"prueba de hu 4","Prioridad":"Alta","Criticidad":"Media","Solicitante":"1dc348ae-ab97-4182-a1e4-b29d684dde2a","EvidenciaInicial":"","FechaDeteccion":"2026-06-30T00:00:00.0000000Z","FechaCreacion":"2026-07-08T19:40:08.4718108Z","ClasificacionFalla":"ConRestriccion","EvaluadoPor":"","EvaluadoEnUtc":"","AprobadoPor":"","AprobadoEnUtc":"","RechazadoPor":"","RechazadoEnUtc":"","MotivoRechazo":"","AnuladoPor":"","AnuladoEnUtc":"","MotivoAnulacion":"","NumeroOT":"","ConvertidoPor":"","ConvertidoEnUtc":"","Observaciones":"Aviso creado en CMMS"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"AvisoId":"AV-000001","Estado":"Aprobado","Tipo":"ApoyoOperacional","FaenaCodigo":"FAE_AND","ActivoCodigo":"PRUEBA-2","Sistema":"","Subsistema":"","Componente":"","Descripcion":"prueba de hu 4","Prioridad":"Alta","Criticidad":"Media","Solicitante":"1dc348ae-ab97-4182-a1e4-b29d684dde2a","EvidenciaInicial":"","FechaDeteccion":"2026-06-30T00:00:00.0000000Z","FechaCreacion":"2026-07-08T19:40:08.4718108Z","ClasificacionFalla":"ConRestriccion","EvaluadoPor":"","EvaluadoEnUtc":"","AprobadoPor":"1dc348ae-ab97-4182-a1e4-b29d684dde2a","AprobadoEnUtc":"2026-07-08T19:44:04.7299442Z","RechazadoPor":"","RechazadoEnUtc":"","MotivoRechazo":"","AnuladoPor":"","AnuladoEnUtc":"","MotivoAnulacion":"","NumeroOT":"","ConvertidoPor":"","ConvertidoEnUtc":"","Observaciones":"Aviso creado en CMMS | Aprobacion: prueba"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M1BQ:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74e9a3a3-aecc-45c0-a59b-6c0dd3bfe1ca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T19:45:29.2878800Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AV-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"AvisoId":"AV-000002","Estado":"Creado","Tipo":"Falla","FaenaCodigo":"FAE_AND","ActivoCodigo":"PRUEBA-2","Sistema":null,"Subsistema":null,"Componente":null,"Descripcion":"prueba de activo no disponible","Prioridad":"Media","Criticidad":"Media","Solicitante":"1dc348ae-ab97-4182-a1e4-b29d684dde2a","EvidenciaInicial":null,"FechaDeteccion":"2026-07-08T00:00:00.0000000Z","FechaCreacion":"2026-07-08T19:45:29.2340779Z","ClasificacionFalla":"SinDetencion","EvaluadoPor":null,"EvaluadoEnUtc":null,"AprobadoPor":null,"AprobadoEnUtc":null,"RechazadoPor":null,"RechazadoEnUtc":null,"MotivoRechazo":null,"AnuladoPor":null,"AnuladoEnUtc":null,"MotivoAnulacion":null,"NumeroOT":null,"ConvertidoPor":null,"ConvertidoEnUtc":null,"Observaciones":"Aviso creado en CMMS"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>prueba de activo no disponible</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT0D92M1CV:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7adcf433-d8ed-454e-b871-0b0cd13a6375</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T20:48:23.5215307Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT62TUJQPE:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7bf6f45a-4748-436d-aa29-6e9667a168d1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T20:50:13.4437698Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT62TUJQPI:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3358e60b-74e8-4505-a8cd-5f1e4ed88293</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T20:55:49.6467267Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>import.applied</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aprobacion de importacion Excel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Importacion aplicada al maestro oficial: plantilla_faenas.xlsx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT62TUJQQM:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11f4f74b-92a1-4da3-a269-1703ec307ffb</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T21:18:57.0214295Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JerarquiaTecnica</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TechnicalHierarchy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIS-MOTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"Codigo":"SIS-MOTOR","Nombre":"Motor","Nivel":"Sistema","CodigoPadre":null,"NombreNormalizado":"MOTOR","FaenaCodigo":"FAE_GM","UbicacionTecnicaCodigo":null,"FamiliasEquipo":null,"ActivosAsignados":null,"AliasHistoricos":null,"Obsoleto":"false","FusionadoEnCodigo":null,"FechaCreacionUtc":"2026-07-08T21:18:56.9642605Z","FechaActualizacionUtc":"2026-07-08T21:18:56.9642605Z"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nodo tecnico creado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT62TUJQTG:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>c29967ac-481e-4958-abe7-03276fd5ac3b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T21:19:32.7206643Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"Codigo":"SIS-MOTOR","Nombre":"Motor","Nivel":"Sistema","CodigoPadre":"","NombreNormalizado":"MOTOR","FaenaCodigo":"FAE_GM","UbicacionTecnicaCodigo":"","FamiliasEquipo":"","ActivosAsignados":"","AliasHistoricos":"","Obsoleto":"false","FusionadoEnCodigo":"","FechaCreacionUtc":"2026-07-08T21:18:56.9642605Z","FechaActualizacionUtc":"2026-07-08T21:18:56.9642605Z"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"Codigo":"SIS-MOTOR","Nombre":"Motor","Nivel":"Sistema","CodigoPadre":null,"NombreNormalizado":"MOTOR","FaenaCodigo":"FAE_GM","UbicacionTecnicaCodigo":null,"FamiliasEquipo":null,"ActivosAsignados":null,"AliasHistoricos":null,"Obsoleto":"false","FusionadoEnCodigo":"","FechaCreacionUtc":"2026-07-08T21:18:56.9642605Z","FechaActualizacionUtc":"2026-07-08T21:19:32.6636326Z"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nodo tecnico actualizado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT62TUJQTK:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b8bc5552-c7b1-4d38-9220-e2954216fd49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T21:24:48.2169472Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUB-LUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"Codigo":"SUB-LUB","Nombre":"Lubricacion","Nivel":"Subsistema","CodigoPadre":"SIS-MOTOR","NombreNormalizado":"LUBRICACION","FaenaCodigo":"FAE_GM","UbicacionTecnicaCodigo":null,"FamiliasEquipo":null,"ActivosAsignados":null,"AliasHistoricos":null,"Obsoleto":"false","FusionadoEnCodigo":null,"FechaCreacionUtc":"2026-07-08T21:24:48.1544478Z","FechaActualizacionUtc":"2026-07-08T21:24:48.1544478Z"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT62TUJQU1:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>e77d958d-e0c2-4ab8-83e7-2c70874bb788</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T21:52:25.7985296Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMT62TUJQUP:00000001</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1894,22 +2068,22 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S126"/>
+  <x:dimension ref="A1:S137"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.139196" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="28.282054" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="37.996339" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22.853482" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13.996339" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="13.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25.996339" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17.853482" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="157.567768" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="12.710625" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="8.567768" style="0" customWidth="1"/>
     <x:col min="10" max="11" width="255" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="14.282054" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="119.139196" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="27.996339" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="30.282054" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="7.853482" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="132.853482" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="28.710625" style="0" customWidth="1"/>
@@ -7043,6 +7217,511 @@
         <x:v>504</x:v>
       </x:c>
     </x:row>
+    <x:row r="127" spans="1:19">
+      <x:c r="A127" s="0" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F127" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G127" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I127" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L127" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M127" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O127" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q127" s="0" t="s">
+        <x:v>507</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:19">
+      <x:c r="A128" s="0" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="E128" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="F128" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G128" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="H128" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="I128" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="K128" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="L128" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M128" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="N128" s="0" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="O128" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q128" s="0" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="S128" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:19">
+      <x:c r="A129" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="E129" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="F129" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G129" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="H129" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="I129" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="J129" s="0" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="K129" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="L129" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M129" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="N129" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="O129" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q129" s="0" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="R129" s="0" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="S129" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:19">
+      <x:c r="A130" s="0" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="E130" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="F130" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G130" s="0" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="H130" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="I130" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="K130" s="0" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="L130" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M130" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="N130" s="0" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="O130" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q130" s="0" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="S130" s="0" t="s">
+        <x:v>526</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:19">
+      <x:c r="A131" s="0" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E131" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F131" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G131" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I131" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L131" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="M131" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="O131" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q131" s="0" t="s">
+        <x:v>531</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:19">
+      <x:c r="A132" s="0" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E132" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F132" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G132" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I132" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L132" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M132" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O132" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q132" s="0" t="s">
+        <x:v>534</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:19">
+      <x:c r="A133" s="0" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="E133" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F133" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G133" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="I133" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="K133" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="L133" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M133" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="N133" s="0" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="O133" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P133" s="0" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="Q133" s="0" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="S133" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:19">
+      <x:c r="A134" s="0" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E134" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="F134" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="G134" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="I134" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="K134" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="L134" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M134" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O134" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P134" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="Q134" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="S134" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:19">
+      <x:c r="A135" s="0" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="E135" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="F135" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="G135" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="I135" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="J135" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="K135" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="L135" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M135" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O135" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P135" s="0" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="Q135" s="0" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="R135" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="S135" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:19">
+      <x:c r="A136" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E136" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="F136" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="G136" s="0" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="I136" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="K136" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="L136" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M136" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O136" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P136" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="Q136" s="0" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="S136" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:19">
+      <x:c r="A137" s="0" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E137" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F137" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G137" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I137" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L137" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M137" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O137" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q137" s="0" t="s">
+        <x:v>562</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/excel/audit_log.xlsx
+++ b/data/excel/audit_log.xlsx
@@ -1703,6 +1703,15 @@
   </x:si>
   <x:si>
     <x:t>0HNMT62TUJQUP:00000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6392fc67-6f24-48f1-8cba-3289f099a4b9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-09T13:41:56.5706358Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0HNMTNVBR5UKF:00000001</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2068,7 +2077,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S137"/>
+  <x:dimension ref="A1:S138"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.139196" style="0" customWidth="1"/>
@@ -7722,6 +7731,44 @@
         <x:v>562</x:v>
       </x:c>
     </x:row>
+    <x:row r="138" spans="1:19">
+      <x:c r="A138" s="0" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E138" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F138" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G138" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I138" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L138" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="M138" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="O138" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q138" s="0" t="s">
+        <x:v>565</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
